--- a/deliverables/traceability/ENG-TRC-001_양방향 요구사항 추적 매트릭스.xlsx
+++ b/deliverables/traceability/ENG-TRC-001_양방향 요구사항 추적 매트릭스.xlsx
@@ -637,31 +637,31 @@
     </row>
     <row r="7" ht="40" customHeight="1">
       <c r="A7" s="29" t="str">
-        <v>Upper Req는 OEM ID(복수 시 세미콜론 구분), SW Req는 SWR ID. Architecture/Detailed Design/Code/SWE.4/SWE.5/SWE.6/Coverage는 이후 단계에서 채움(Phase 1 SWE.1 시점 의도적 공란).</v>
+        <v>Upper Req는 OEM ID(복수 시 세미콜론 구분), SW Req는 SWR ID. Architecture는 CMP-ID(세미콜론 구분, ENG-SWE2-001 §3.1/§12 참조)로 SWR 20건 전체를 채웠다(G2 설계 단계, 2026-09-18). Detailed Design/Code/SWE.4/SWE.5/SWE.6/Coverage는 Phase 1 대상 7건(SWR-005~009,013,021)은 상세설계 단계, 나머지 13건은 Phase 2/3에서 채워지므로 의도적 공란으로 유지한다.</v>
       </c>
       <c r="B7" s="30" t="str">
-        <v>Upper Req는 OEM ID(복수 시 세미콜론 구분), SW Req는 SWR ID. Architecture/Detailed Design/Code/SWE.4/SWE.5/SWE.6/Coverage는 이후 단계에서 채움(Phase 1 SWE.1 시점 의도적 공란).</v>
+        <v>Upper Req는 OEM ID(복수 시 세미콜론 구분), SW Req는 SWR ID. Architecture는 CMP-ID(세미콜론 구분, ENG-SWE2-001 §3.1/§12 참조)로 SWR 20건 전체를 채웠다(G2 설계 단계, 2026-09-18). Detailed Design/Code/SWE.4/SWE.5/SWE.6/Coverage는 Phase 1 대상 7건(SWR-005~009,013,021)은 상세설계 단계, 나머지 13건은 Phase 2/3에서 채워지므로 의도적 공란으로 유지한다.</v>
       </c>
       <c r="C7" s="30" t="str">
-        <v>Upper Req는 OEM ID(복수 시 세미콜론 구분), SW Req는 SWR ID. Architecture/Detailed Design/Code/SWE.4/SWE.5/SWE.6/Coverage는 이후 단계에서 채움(Phase 1 SWE.1 시점 의도적 공란).</v>
+        <v>Upper Req는 OEM ID(복수 시 세미콜론 구분), SW Req는 SWR ID. Architecture는 CMP-ID(세미콜론 구분, ENG-SWE2-001 §3.1/§12 참조)로 SWR 20건 전체를 채웠다(G2 설계 단계, 2026-09-18). Detailed Design/Code/SWE.4/SWE.5/SWE.6/Coverage는 Phase 1 대상 7건(SWR-005~009,013,021)은 상세설계 단계, 나머지 13건은 Phase 2/3에서 채워지므로 의도적 공란으로 유지한다.</v>
       </c>
       <c r="D7" s="30" t="str">
-        <v>Upper Req는 OEM ID(복수 시 세미콜론 구분), SW Req는 SWR ID. Architecture/Detailed Design/Code/SWE.4/SWE.5/SWE.6/Coverage는 이후 단계에서 채움(Phase 1 SWE.1 시점 의도적 공란).</v>
+        <v>Upper Req는 OEM ID(복수 시 세미콜론 구분), SW Req는 SWR ID. Architecture는 CMP-ID(세미콜론 구분, ENG-SWE2-001 §3.1/§12 참조)로 SWR 20건 전체를 채웠다(G2 설계 단계, 2026-09-18). Detailed Design/Code/SWE.4/SWE.5/SWE.6/Coverage는 Phase 1 대상 7건(SWR-005~009,013,021)은 상세설계 단계, 나머지 13건은 Phase 2/3에서 채워지므로 의도적 공란으로 유지한다.</v>
       </c>
       <c r="E7" s="30" t="str">
-        <v>Upper Req는 OEM ID(복수 시 세미콜론 구분), SW Req는 SWR ID. Architecture/Detailed Design/Code/SWE.4/SWE.5/SWE.6/Coverage는 이후 단계에서 채움(Phase 1 SWE.1 시점 의도적 공란).</v>
+        <v>Upper Req는 OEM ID(복수 시 세미콜론 구분), SW Req는 SWR ID. Architecture는 CMP-ID(세미콜론 구분, ENG-SWE2-001 §3.1/§12 참조)로 SWR 20건 전체를 채웠다(G2 설계 단계, 2026-09-18). Detailed Design/Code/SWE.4/SWE.5/SWE.6/Coverage는 Phase 1 대상 7건(SWR-005~009,013,021)은 상세설계 단계, 나머지 13건은 Phase 2/3에서 채워지므로 의도적 공란으로 유지한다.</v>
       </c>
       <c r="F7" s="30" t="str">
-        <v>Upper Req는 OEM ID(복수 시 세미콜론 구분), SW Req는 SWR ID. Architecture/Detailed Design/Code/SWE.4/SWE.5/SWE.6/Coverage는 이후 단계에서 채움(Phase 1 SWE.1 시점 의도적 공란).</v>
+        <v>Upper Req는 OEM ID(복수 시 세미콜론 구분), SW Req는 SWR ID. Architecture는 CMP-ID(세미콜론 구분, ENG-SWE2-001 §3.1/§12 참조)로 SWR 20건 전체를 채웠다(G2 설계 단계, 2026-09-18). Detailed Design/Code/SWE.4/SWE.5/SWE.6/Coverage는 Phase 1 대상 7건(SWR-005~009,013,021)은 상세설계 단계, 나머지 13건은 Phase 2/3에서 채워지므로 의도적 공란으로 유지한다.</v>
       </c>
       <c r="G7" s="30" t="str">
-        <v>Upper Req는 OEM ID(복수 시 세미콜론 구분), SW Req는 SWR ID. Architecture/Detailed Design/Code/SWE.4/SWE.5/SWE.6/Coverage는 이후 단계에서 채움(Phase 1 SWE.1 시점 의도적 공란).</v>
+        <v>Upper Req는 OEM ID(복수 시 세미콜론 구분), SW Req는 SWR ID. Architecture는 CMP-ID(세미콜론 구분, ENG-SWE2-001 §3.1/§12 참조)로 SWR 20건 전체를 채웠다(G2 설계 단계, 2026-09-18). Detailed Design/Code/SWE.4/SWE.5/SWE.6/Coverage는 Phase 1 대상 7건(SWR-005~009,013,021)은 상세설계 단계, 나머지 13건은 Phase 2/3에서 채워지므로 의도적 공란으로 유지한다.</v>
       </c>
       <c r="H7" s="30" t="str">
-        <v>Upper Req는 OEM ID(복수 시 세미콜론 구분), SW Req는 SWR ID. Architecture/Detailed Design/Code/SWE.4/SWE.5/SWE.6/Coverage는 이후 단계에서 채움(Phase 1 SWE.1 시점 의도적 공란).</v>
+        <v>Upper Req는 OEM ID(복수 시 세미콜론 구분), SW Req는 SWR ID. Architecture는 CMP-ID(세미콜론 구분, ENG-SWE2-001 §3.1/§12 참조)로 SWR 20건 전체를 채웠다(G2 설계 단계, 2026-09-18). Detailed Design/Code/SWE.4/SWE.5/SWE.6/Coverage는 Phase 1 대상 7건(SWR-005~009,013,021)은 상세설계 단계, 나머지 13건은 Phase 2/3에서 채워지므로 의도적 공란으로 유지한다.</v>
       </c>
       <c r="I7" s="31" t="str">
-        <v>Upper Req는 OEM ID(복수 시 세미콜론 구분), SW Req는 SWR ID. Architecture/Detailed Design/Code/SWE.4/SWE.5/SWE.6/Coverage는 이후 단계에서 채움(Phase 1 SWE.1 시점 의도적 공란).</v>
+        <v>Upper Req는 OEM ID(복수 시 세미콜론 구분), SW Req는 SWR ID. Architecture는 CMP-ID(세미콜론 구분, ENG-SWE2-001 §3.1/§12 참조)로 SWR 20건 전체를 채웠다(G2 설계 단계, 2026-09-18). Detailed Design/Code/SWE.4/SWE.5/SWE.6/Coverage는 Phase 1 대상 7건(SWR-005~009,013,021)은 상세설계 단계, 나머지 13건은 Phase 2/3에서 채워지므로 의도적 공란으로 유지한다.</v>
       </c>
     </row>
     <row r="9" ht="32" customHeight="1">
@@ -700,7 +700,9 @@
       <c r="B10" s="42" t="str">
         <v>SWR-001</v>
       </c>
-      <c r="C10" s="42" t="str"/>
+      <c r="C10" s="42" t="str">
+        <v>CMP-02; CMP-07; CMP-19</v>
+      </c>
       <c r="D10" s="42" t="str"/>
       <c r="E10" s="42" t="str"/>
       <c r="F10" s="42" t="str"/>
@@ -715,7 +717,9 @@
       <c r="B11" s="42" t="str">
         <v>SWR-002</v>
       </c>
-      <c r="C11" s="42" t="str"/>
+      <c r="C11" s="42" t="str">
+        <v>CMP-19</v>
+      </c>
       <c r="D11" s="42" t="str"/>
       <c r="E11" s="42" t="str"/>
       <c r="F11" s="42" t="str"/>
@@ -730,7 +734,9 @@
       <c r="B12" s="42" t="str">
         <v>SWR-003</v>
       </c>
-      <c r="C12" s="42" t="str"/>
+      <c r="C12" s="42" t="str">
+        <v>CMP-18</v>
+      </c>
       <c r="D12" s="42" t="str"/>
       <c r="E12" s="42" t="str"/>
       <c r="F12" s="42" t="str"/>
@@ -745,7 +751,9 @@
       <c r="B13" s="42" t="str">
         <v>SWR-004</v>
       </c>
-      <c r="C13" s="42" t="str"/>
+      <c r="C13" s="42" t="str">
+        <v>CMP-02; CMP-19</v>
+      </c>
       <c r="D13" s="42" t="str"/>
       <c r="E13" s="42" t="str"/>
       <c r="F13" s="42" t="str"/>
@@ -760,7 +768,9 @@
       <c r="B14" s="42" t="str">
         <v>SWR-005</v>
       </c>
-      <c r="C14" s="42" t="str"/>
+      <c r="C14" s="42" t="str">
+        <v>CMP-14</v>
+      </c>
       <c r="D14" s="42" t="str"/>
       <c r="E14" s="42" t="str"/>
       <c r="F14" s="42" t="str"/>
@@ -775,7 +785,9 @@
       <c r="B15" s="42" t="str">
         <v>SWR-006</v>
       </c>
-      <c r="C15" s="42" t="str"/>
+      <c r="C15" s="42" t="str">
+        <v>CMP-14</v>
+      </c>
       <c r="D15" s="42" t="str"/>
       <c r="E15" s="42" t="str"/>
       <c r="F15" s="42" t="str"/>
@@ -790,7 +802,9 @@
       <c r="B16" s="42" t="str">
         <v>SWR-007</v>
       </c>
-      <c r="C16" s="42" t="str"/>
+      <c r="C16" s="42" t="str">
+        <v>CMP-13</v>
+      </c>
       <c r="D16" s="42" t="str"/>
       <c r="E16" s="42" t="str"/>
       <c r="F16" s="42" t="str"/>
@@ -805,7 +819,9 @@
       <c r="B17" s="42" t="str">
         <v>SWR-008</v>
       </c>
-      <c r="C17" s="42" t="str"/>
+      <c r="C17" s="42" t="str">
+        <v>CMP-13</v>
+      </c>
       <c r="D17" s="42" t="str"/>
       <c r="E17" s="42" t="str"/>
       <c r="F17" s="42" t="str"/>
@@ -820,7 +836,9 @@
       <c r="B18" s="42" t="str">
         <v>SWR-009</v>
       </c>
-      <c r="C18" s="42" t="str"/>
+      <c r="C18" s="42" t="str">
+        <v>CMP-14</v>
+      </c>
       <c r="D18" s="42" t="str"/>
       <c r="E18" s="42" t="str"/>
       <c r="F18" s="42" t="str"/>
@@ -835,7 +853,9 @@
       <c r="B19" s="42" t="str">
         <v>SWR-010</v>
       </c>
-      <c r="C19" s="42" t="str"/>
+      <c r="C19" s="42" t="str">
+        <v>CMP-06</v>
+      </c>
       <c r="D19" s="42" t="str"/>
       <c r="E19" s="42" t="str"/>
       <c r="F19" s="42" t="str"/>
@@ -850,7 +870,9 @@
       <c r="B20" s="42" t="str">
         <v>SWR-011</v>
       </c>
-      <c r="C20" s="42" t="str"/>
+      <c r="C20" s="42" t="str">
+        <v>CMP-06</v>
+      </c>
       <c r="D20" s="42" t="str"/>
       <c r="E20" s="42" t="str"/>
       <c r="F20" s="42" t="str"/>
@@ -865,7 +887,9 @@
       <c r="B21" s="42" t="str">
         <v>SWR-012</v>
       </c>
-      <c r="C21" s="42" t="str"/>
+      <c r="C21" s="42" t="str">
+        <v>CMP-06; CMP-21</v>
+      </c>
       <c r="D21" s="42" t="str"/>
       <c r="E21" s="42" t="str"/>
       <c r="F21" s="42" t="str"/>
@@ -880,7 +904,9 @@
       <c r="B22" s="42" t="str">
         <v>SWR-013</v>
       </c>
-      <c r="C22" s="42" t="str"/>
+      <c r="C22" s="42" t="str">
+        <v>CMP-07; CMP-08; CMP-10</v>
+      </c>
       <c r="D22" s="42" t="str"/>
       <c r="E22" s="42" t="str"/>
       <c r="F22" s="42" t="str"/>
@@ -895,7 +921,9 @@
       <c r="B23" s="42" t="str">
         <v>SWR-014</v>
       </c>
-      <c r="C23" s="42" t="str"/>
+      <c r="C23" s="42" t="str">
+        <v>CMP-03; CMP-20</v>
+      </c>
       <c r="D23" s="42" t="str"/>
       <c r="E23" s="42" t="str"/>
       <c r="F23" s="42" t="str"/>
@@ -910,7 +938,9 @@
       <c r="B24" s="42" t="str">
         <v>SWR-015</v>
       </c>
-      <c r="C24" s="42" t="str"/>
+      <c r="C24" s="42" t="str">
+        <v>CMP-03; CMP-20</v>
+      </c>
       <c r="D24" s="42" t="str"/>
       <c r="E24" s="42" t="str"/>
       <c r="F24" s="42" t="str"/>
@@ -925,7 +955,9 @@
       <c r="B25" s="42" t="str">
         <v>SWR-016</v>
       </c>
-      <c r="C25" s="42" t="str"/>
+      <c r="C25" s="42" t="str">
+        <v>CMP-05; CMP-11; CMP-12</v>
+      </c>
       <c r="D25" s="42" t="str"/>
       <c r="E25" s="42" t="str"/>
       <c r="F25" s="42" t="str"/>
@@ -940,7 +972,9 @@
       <c r="B26" s="42" t="str">
         <v>SWR-017</v>
       </c>
-      <c r="C26" s="42" t="str"/>
+      <c r="C26" s="42" t="str">
+        <v>CMP-15</v>
+      </c>
       <c r="D26" s="42" t="str"/>
       <c r="E26" s="42" t="str"/>
       <c r="F26" s="42" t="str"/>
@@ -955,7 +989,9 @@
       <c r="B27" s="42" t="str">
         <v>SWR-018</v>
       </c>
-      <c r="C27" s="42" t="str"/>
+      <c r="C27" s="42" t="str">
+        <v>CMP-16</v>
+      </c>
       <c r="D27" s="42" t="str"/>
       <c r="E27" s="42" t="str"/>
       <c r="F27" s="42" t="str"/>
@@ -970,7 +1006,9 @@
       <c r="B28" s="42" t="str">
         <v>SWR-020</v>
       </c>
-      <c r="C28" s="42" t="str"/>
+      <c r="C28" s="42" t="str">
+        <v>CMP-10; CMP-17</v>
+      </c>
       <c r="D28" s="42" t="str"/>
       <c r="E28" s="42" t="str"/>
       <c r="F28" s="42" t="str"/>
@@ -985,7 +1023,9 @@
       <c r="B29" s="42" t="str">
         <v>SWR-021</v>
       </c>
-      <c r="C29" s="42" t="str"/>
+      <c r="C29" s="42" t="str">
+        <v>CMP-09; CMP-10</v>
+      </c>
       <c r="D29" s="42" t="str"/>
       <c r="E29" s="42" t="str"/>
       <c r="F29" s="42" t="str"/>
